--- a/engine/publish_queue/PHDC/PHDC_Valuation_Model_10092026.xlsx
+++ b/engine/publish_queue/PHDC/PHDC_Valuation_Model_10092026.xlsx
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.2608706403474768</v>
+        <v>0.2583068424344719</v>
       </c>
     </row>
     <row r="22">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.2510196958005933</v>
+        <v>0.249647238833035</v>
       </c>
     </row>
     <row r="23">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.2608706403474768</v>
+        <v>0.2583068424344719</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>

--- a/engine/publish_queue/PHDC/PHDC_Valuation_Model_10092026.xlsx
+++ b/engine/publish_queue/PHDC/PHDC_Valuation_Model_10092026.xlsx
@@ -522,7 +522,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edition of 2 September 2026. Supersedes 30 August 2026.</t>
+          <t>Edition of 10 September 2026. Supersedes 3 September 2026.</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>-Assumptions!B13</f>
+        <f>-Assumptions!B14</f>
         <v/>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>Assumptions!B14</f>
+        <f>Assumptions!B15</f>
         <v/>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>Assumptions!B15</f>
+        <f>Assumptions!B16</f>
         <v/>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>-B10*Assumptions!B16</f>
+        <f>-B10*Assumptions!B17</f>
         <v/>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>Assumptions!B17</f>
+        <f>Assumptions!B18</f>
         <v/>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6152,11 +6152,11 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.3832237248431056</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>average of FY2025 and 1Q2026 as reported</t>
+          <t>the first quarter of 2026 on its own, the latest disclosure; NOT an average (FY2025 was 41.16%, 1Q2026 35.48%)</t>
         </is>
       </c>
     </row>
@@ -6197,67 +6197,67 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>below nominal growth, stated</t>
+          <t>the terminal growth this model runs, read from the valuation module</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital</t>
+          <t>Cost of capital — ADOPTED (traded default-swap basis)</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.2583068424344719</v>
+        <v>0.249647238833035</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>built on the Fundamental Valuation and Peer sheets</t>
+          <t>the rate this model discounts at; section 1.8 marks it adopted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Net debt (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>23244.718678</v>
+          <t>Cost of capital — alternative (credit-rating basis), not used</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0.2583068424344719</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>gross borrowings less cash, 31 March 2026 reviewed balance sheet</t>
+          <t>published for comparison only; no cell on this sheet reads it</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Investments in associates (EGP mn)</t>
+          <t>Net debt (EGP mn)</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>3838.697211</v>
+        <v>23244.718678</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31 March 2026 reviewed balance sheet</t>
+          <t>gross borrowings less cash, 31 March 2026 reviewed balance sheet</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Investment property (EGP mn)</t>
+          <t>Investments in associates (EGP mn)</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>1020.474869</v>
+        <v>3838.697211</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -6268,197 +6268,212 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Minority interests, share of equity value</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>0.0468375604683756</v>
+          <t>Investment property (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>1020.474869</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>the minority's filed share of FY2025 profit after tax, as its share of value</t>
+          <t>31 March 2026 reviewed balance sheet</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>2859.92</v>
+          <t>Minority interests, share of equity value</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.0468375604683756</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>the minority's filed share of FY2025 profit after tax, as its share of value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Opening revenue (EGP mn)</t>
+          <t>Shares outstanding (mn)</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>36169.3</v>
+        <v>2859.92</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>FY2025 audited</t>
+          <t>FY2025</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Opening order book (EGP mn)</t>
+          <t>Opening revenue (EGP mn)</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>263000</v>
+        <v>36169.3</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>as at 31 March 2026</t>
+          <t>FY2025 audited</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Units delivered, 2026</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
-        <v>2035.093098749406</v>
+          <t>Opening order book (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>263000</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>implied by the reported first quarter of 2026</t>
+          <t>as at 31 March 2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Units delivered, annual growth</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>0.15</v>
+          <t>Units delivered, 2026</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>2035.093098749406</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>the disclosed run of handovers, 1,308 / 1,281 / 1,500 / 2,000</t>
+          <t>implied by the reported first quarter of 2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Revenue per delivered unit, 2026 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>19.727806568</v>
+          <t>Units delivered, annual growth</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0.15</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>FY2024 revenue over c. 2,000 units delivered, escalated</t>
+          <t>the disclosed run of handovers, 1,308 / 1,281 / 1,500 / 2,000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Revenue per delivered unit, 2026 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>19.727806568</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 revenue over c. 2,000 units delivered, escalated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Maintenance capital expenditure, share of revenue</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B24" s="12" t="n">
         <v>0.01</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>the building itself is inventory and sits in operating cash</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>NOT DISCLOSED — absent by design, never estimated</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>cash flow statement detail</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>The FY2025 cash-flow statement is published in its three totals only (operating EGP 1,424.2mn, investing EGP -4,031.7mn, financing EGP 5,628.8mn); no line-by-line statement is post</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>fy2025 results release</t>
+          <t>cash flow statement detail</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PHD has published FY2025 consolidated statements but NO FY2025 full-year results release. The release is where units sold, new sales, deliveries and construction spend are disclose</t>
+          <t>The FY2025 cash-flow statement is published in its three totals only (operating EGP 1,424.2mn, investing EGP -4,031.7mn, financing EGP 5,628.8mn); no line-by-line statement is post</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>h1 2026 results</t>
+          <t>fy2025 results release</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>As at this build date (30-Aug-2026) no 2Q/H1-2026 statements or release are posted to the result centre; the newest disclosure of any kind is 1Q2026 (posted 25-Jun-2026). The study</t>
+          <t>PHD has published FY2025 consolidated statements but NO FY2025 full-year results release. The release is where units sold, new sales, deliveries and construction spend are disclose</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>securitisation pricing</t>
+          <t>h1 2026 results</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>The EGP 2.015bn securitisation of 4-Feb-2026 discloses tranche sizes, tenors and national-scale ratings but NO coupon on any tranche, so the company's own marginal cost of debt can</t>
+          <t>A half-year 2026 release of 18-Aug-2026 is REPORTED in the trade press — an order book of EGP 284bn at 30 June, 40% up on the year, and a further EGP 75bn sold at Hacienda Ras El H</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>per project pricing</t>
+          <t>securitisation pricing</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The company does not disclose per-project unit mix, average unit area, price per square metre or construction cost per square metre. The 11-Jun-2026 edition carried a full per-proj</t>
+          <t>The EGP 2.015bn securitisation of 4-Feb-2026 discloses tranche sizes, tenors and national-scale ratings but NO coupon on any tranche, so the company's own marginal cost of debt can</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>per project pricing</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>The company does not disclose per-project unit mix, average unit area, price per square metre or construction cost per square metre. The 11-Jun-2026 edition carried a full per-proj</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>backlog cost to complete</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Remaining construction cost against the EGP 263bn backlog is not disclosed as a single figure. It is inferred in the model from the realised gross margin and flagged where used.</t>
         </is>
@@ -6553,7 +6568,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>-(B4+B5+B6+B7+B8)*Assumptions!B16</f>
+        <f>-(B4+B5+B6+B7+B8)*Assumptions!B17</f>
         <v/>
       </c>
     </row>
@@ -6575,7 +6590,7 @@
         </is>
       </c>
       <c r="B11" s="7">
-        <f>B10/Assumptions!B17</f>
+        <f>B10/Assumptions!B18</f>
         <v/>
       </c>
     </row>
@@ -7421,7 +7436,7 @@
         </is>
       </c>
       <c r="B7" s="21">
-        <f>Assumptions!$B$20</f>
+        <f>Assumptions!$B$21</f>
         <v/>
       </c>
       <c r="C7" s="21">
@@ -7488,7 +7503,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>Assumptions!$B$22</f>
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="C8" s="7">
@@ -7823,63 +7838,63 @@
         </is>
       </c>
       <c r="B13" s="21">
-        <f>-B9*Assumptions!$B$23</f>
+        <f>-B9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="C13" s="21">
-        <f>-C9*Assumptions!$B$23</f>
+        <f>-C9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>-D9*Assumptions!$B$23</f>
+        <f>-D9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="E13" s="21">
-        <f>-E9*Assumptions!$B$23</f>
+        <f>-E9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>-F9*Assumptions!$B$23</f>
+        <f>-F9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="G13" s="21">
-        <f>-G9*Assumptions!$B$23</f>
+        <f>-G9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="H13" s="21">
-        <f>-H9*Assumptions!$B$23</f>
+        <f>-H9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="I13" s="21">
-        <f>-I9*Assumptions!$B$23</f>
+        <f>-I9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="J13" s="21">
-        <f>-J9*Assumptions!$B$23</f>
+        <f>-J9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="K13" s="21">
-        <f>-K9*Assumptions!$B$23</f>
+        <f>-K9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="L13" s="21">
-        <f>-L9*Assumptions!$B$23</f>
+        <f>-L9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="M13" s="21">
-        <f>-M9*Assumptions!$B$23</f>
+        <f>-M9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="N13" s="21">
-        <f>-N9*Assumptions!$B$23</f>
+        <f>-N9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="O13" s="21">
-        <f>-O9*Assumptions!$B$23</f>
+        <f>-O9*Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="P13" s="21">
-        <f>-P9*Assumptions!$B$23</f>
+        <f>-P9*Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
